--- a/data/trans_bre/P2A_ner_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Edad-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 2,36</t>
+          <t>-5,34; 1,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,6</t>
+          <t>1,31; 7,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 1,61</t>
+          <t>-5,08; 1,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 11,44</t>
+          <t>0,07; 11,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 240,86</t>
+          <t>-100,0; 315,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-53,35; 1945,68</t>
+          <t>-44,71; 1262,26</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 1,72</t>
+          <t>-2,52; 1,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,49</t>
+          <t>-1,16; 3,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 0,48</t>
+          <t>-5,43; 0,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 4,26</t>
+          <t>-3,67; 4,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,12; 191,36</t>
+          <t>-79,17; 247,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,85; 725,26</t>
+          <t>-76,27; 689,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-84,74; 26,12</t>
+          <t>-84,71; 39,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-54,06; 120,36</t>
+          <t>-52,23; 103,37</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 4,9</t>
+          <t>-4,28; 5,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 7,02</t>
+          <t>-0,59; 7,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 4,32</t>
+          <t>-5,19; 4,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 7,11</t>
+          <t>-1,07; 7,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-80,66; 271,78</t>
+          <t>-79,09; 331,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-97,73; —</t>
+          <t>-69,94; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-57,0; 138,74</t>
+          <t>-59,84; 121,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,37; 274,24</t>
+          <t>-22,71; 246,81</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 1,76</t>
+          <t>-3,42; 2,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 3,31</t>
+          <t>-2,95; 3,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 11,03</t>
+          <t>0,32; 11,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,17; -0,19</t>
+          <t>-7,33; -0,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-88,43; 166,86</t>
+          <t>-87,69; 170,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,23; 383,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 496,08</t>
+          <t>-3,37; 493,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,98; -1,79</t>
+          <t>-74,1; 0,91</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,87</t>
+          <t>-2,13; 0,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,37</t>
+          <t>0,07; 3,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,26</t>
+          <t>-1,83; 2,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,79</t>
+          <t>-2,48; 1,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-59,06; 50,99</t>
+          <t>-60,02; 51,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 423,77</t>
+          <t>-5,64; 386,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-32,91; 59,16</t>
+          <t>-31,89; 69,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,08; 38,48</t>
+          <t>-36,51; 33,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Edad-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 1,78</t>
+          <t>-5,4; 2,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,27</t>
+          <t>1,28; 7,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 1,66</t>
+          <t>-5,16; 1,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 11,86</t>
+          <t>-0,14; 11,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 315,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,71; 1262,26</t>
+          <t>-34,81; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,9</t>
+          <t>-2,84; 1,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,53</t>
+          <t>-1,15; 3,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 0,79</t>
+          <t>-5,58; 0,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 4,0</t>
+          <t>-3,49; 4,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,17; 247,27</t>
+          <t>-83,96; 183,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,27; 689,21</t>
+          <t>-69,41; 718,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-84,71; 39,21</t>
+          <t>-85,83; 24,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,23; 103,37</t>
+          <t>-48,45; 119,32</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 5,01</t>
+          <t>-4,5; 5,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 7,67</t>
+          <t>-0,64; 7,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 4,11</t>
+          <t>-6,0; 4,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 7,09</t>
+          <t>-1,55; 7,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-79,09; 331,45</t>
+          <t>-79,6; 308,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-69,94; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-59,84; 121,13</t>
+          <t>-63,17; 115,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,71; 246,81</t>
+          <t>-29,12; 281,84</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 2,08</t>
+          <t>-3,51; 1,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 3,55</t>
+          <t>-3,16; 3,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 11,01</t>
+          <t>0,82; 11,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,33; -0,27</t>
+          <t>-7,12; -0,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-87,69; 170,14</t>
+          <t>-84,09; 161,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-84,23; 383,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 493,44</t>
+          <t>2,27; 456,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,1; 0,91</t>
+          <t>-73,83; -0,53</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,93</t>
+          <t>-2,07; 1,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 3,22</t>
+          <t>0,19; 3,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,56</t>
+          <t>-1,99; 2,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 1,6</t>
+          <t>-2,28; 1,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-60,02; 51,67</t>
+          <t>-60,37; 56,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 386,7</t>
+          <t>2,47; 391,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 69,55</t>
+          <t>-34,43; 66,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-36,51; 33,81</t>
+          <t>-33,39; 41,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,6</t>
+          <t>4,65</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>213,75%</t>
+          <t>231,55%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 2,29</t>
+          <t>-5,29; 2,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,92</t>
+          <t>1,3; 7,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 1,6</t>
+          <t>-5,39; 1,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 11,4</t>
+          <t>0,21; 11,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 240,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-34,81; —</t>
+          <t>-54,24; 2094,69</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 1,67</t>
+          <t>-2,83; 1,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,4</t>
+          <t>-1,12; 3,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 0,5</t>
+          <t>-6,04; 0,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 4,27</t>
+          <t>-3,45; 5,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-83,96; 183,2</t>
+          <t>-82,12; 191,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,41; 718,18</t>
+          <t>-71,85; 725,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-85,83; 24,11</t>
+          <t>-84,74; 26,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,45; 119,32</t>
+          <t>-46,92; 141,86</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>2,95</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>64,34%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 5,01</t>
+          <t>-4,17; 4,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 7,39</t>
+          <t>-0,64; 7,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 4,03</t>
+          <t>-5,01; 4,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 7,0</t>
+          <t>-1,37; 7,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-79,6; 308,72</t>
+          <t>-80,66; 271,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-97,73; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-63,17; 115,29</t>
+          <t>-57,0; 138,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-29,12; 281,84</t>
+          <t>-25,31; 264,73</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,61</t>
+          <t>-3,54</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-47,99%</t>
+          <t>-44,63%</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 1,9</t>
+          <t>-3,86; 1,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 3,09</t>
+          <t>-3,35; 3,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 11,15</t>
+          <t>0,17; 11,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,12; -0,22</t>
+          <t>-7,29; 0,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,09; 161,56</t>
+          <t>-88,43; 166,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 456,24</t>
+          <t>-6,27; 496,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,83; -0,53</t>
+          <t>-70,89; 5,87</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-5,94%</t>
+          <t>-1,87%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,03</t>
+          <t>-2,11; 0,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,32</t>
+          <t>0,19; 3,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,5</t>
+          <t>-1,92; 2,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,9</t>
+          <t>-2,39; 2,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-60,37; 56,46</t>
+          <t>-59,06; 50,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 391,45</t>
+          <t>3,81; 423,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-34,43; 66,33</t>
+          <t>-32,91; 59,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-33,39; 41,64</t>
+          <t>-33,13; 43,22</t>
         </is>
       </c>
     </row>
